--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.9_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.9_RTO_Pretty.xlsx
@@ -3133,7 +3133,7 @@
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>SRSR10102507</t>
+          <t>SRGB10952551</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="166">
       <c r="A166" s="36" t="inlineStr">
         <is>
-          <t>SRBG10020907</t>
+          <t>SRBG10720948</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -9712,7 +9712,7 @@
     <row r="169">
       <c r="A169" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100955A</t>
+          <t>SRGB10420992</t>
         </is>
       </c>
       <c r="B169" s="30" t="inlineStr">
@@ -9763,7 +9763,7 @@
     <row r="170">
       <c r="A170" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100955B</t>
+          <t>SRGB10380919</t>
         </is>
       </c>
       <c r="B170" s="29" t="inlineStr">
